--- a/SampleExcelFiles/GenericTypeSampleMetadata.xlsx
+++ b/SampleExcelFiles/GenericTypeSampleMetadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/External/Projects/GitHub/UniSharper.Data.Metadata/SampleExcelFiles/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/External/Projects/GitHub/UniSharper.Data.Metadata/master/SampleExcelFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EEC5AFF-7278-A346-84D1-FD52197B7DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40F8075-F2DC-0D41-9C53-9917C1D78FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -132,10 +132,6 @@
     <t>4|5|6|7</t>
   </si>
   <si>
-    <t>ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>enum</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -432,6 +428,10 @@
   </si>
   <si>
     <t>Ignored Data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -940,86 +940,86 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="30" customHeight="1">
@@ -1052,7 +1052,7 @@
         <v>7</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>8</v>
@@ -1067,7 +1067,7 @@
         <v>11</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q2" s="4" t="s">
         <v>25</v>
@@ -1111,91 +1111,91 @@
     </row>
     <row r="3" spans="1:29" ht="30" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="K3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="P3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="Q3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="R3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="S3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="V3" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="R3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="U3" s="5" t="s">
+      <c r="W3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="V3" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="W3" s="5" t="s">
+      <c r="X3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="X3" s="5" t="s">
+      <c r="Y3" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="Y3" s="5" t="s">
+      <c r="Z3" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="Z3" s="5" t="s">
+      <c r="AA3" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AA3" s="5" t="s">
+      <c r="AB3" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AB3" s="5" t="s">
+      <c r="AC3" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="AC3" s="5" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="30" customHeight="1">
@@ -1209,13 +1209,13 @@
         <v>1</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="G4" s="5">
         <v>-32768</v>
@@ -1245,46 +1245,46 @@
         <v>9.9999999999999908E+27</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R4" s="5" t="s">
         <v>28</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="U4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="V4" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="V4" s="9" t="s">
+      <c r="W4" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="W4" s="5" t="s">
-        <v>68</v>
       </c>
       <c r="X4" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Y4" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Z4" s="5" t="s">
         <v>31</v>
       </c>
       <c r="AA4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB4" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="AB4" s="5" t="s">
+      <c r="AC4" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="AC4" s="5" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/SampleExcelFiles/GenericTypeSampleMetadata.xlsx
+++ b/SampleExcelFiles/GenericTypeSampleMetadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/External/Projects/GitHub/UniSharper.Data.Metadata/master/SampleExcelFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40F8075-F2DC-0D41-9C53-9917C1D78FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70348858-380C-A845-A4EF-45BBD6065A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1480" yWindow="1660" windowWidth="38400" windowHeight="19200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -117,9 +117,6 @@
     <t>ID</t>
   </si>
   <si>
-    <t>dsaweq你好！@#￥%……&amp;*（）</t>
-  </si>
-  <si>
     <t>TRUE|false|0|1</t>
   </si>
   <si>
@@ -432,6 +429,10 @@
   </si>
   <si>
     <t>Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dsaweq你好！@#￥%……&amp;*（）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -901,7 +902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="20.6640625" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.6640625" style="3" customWidth="1"/>
@@ -940,86 +941,86 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="30" customHeight="1">
@@ -1052,7 +1053,7 @@
         <v>7</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>8</v>
@@ -1067,7 +1068,7 @@
         <v>11</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q2" s="4" t="s">
         <v>25</v>
@@ -1111,180 +1112,211 @@
     </row>
     <row r="3" spans="1:29" ht="30" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="K3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="P3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="Q3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="R3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="S3" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="V3" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="R3" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="U3" s="5" t="s">
+      <c r="W3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="V3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="W3" s="5" t="s">
+      <c r="X3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="X3" s="5" t="s">
+      <c r="Y3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="Y3" s="5" t="s">
+      <c r="Z3" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="Z3" s="5" t="s">
+      <c r="AA3" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AA3" s="5" t="s">
+      <c r="AB3" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AB3" s="5" t="s">
+      <c r="AC3" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="AC3" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="30" customHeight="1">
-      <c r="A4" s="5">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="5"/>
+    </row>
+    <row r="5" spans="1:29" ht="30" customHeight="1">
+      <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B5" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="5">
+        <v>-32768</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2147483647</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="6">
+        <v>-922337203685477</v>
+      </c>
+      <c r="L5" s="7">
+        <v>922337203685477</v>
+      </c>
+      <c r="M5" s="8">
+        <v>3.4548214832139799</v>
+      </c>
+      <c r="N5" s="5">
+        <v>10.0214510024561</v>
+      </c>
+      <c r="O5" s="6">
+        <v>9.9999999999999908E+27</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="R5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4" s="5">
-        <v>-32768</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>2147483647</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="6">
-        <v>-922337203685477</v>
-      </c>
-      <c r="L4" s="7">
-        <v>922337203685477</v>
-      </c>
-      <c r="M4" s="8">
-        <v>3.4548214832139799</v>
-      </c>
-      <c r="N4" s="5">
-        <v>10.0214510024561</v>
-      </c>
-      <c r="O4" s="6">
-        <v>9.9999999999999908E+27</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="R4" s="5" t="s">
+      <c r="S5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="T5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="S4" s="5" t="s">
+      <c r="U5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="T4" s="5" t="s">
+      <c r="V5" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="U4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="V4" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="W4" s="5" t="s">
+      <c r="Y5" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="Z5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="Y4" s="5" t="s">
+      <c r="AA5" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="Z4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA4" s="5" t="s">
+      <c r="AB5" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="AB4" s="5" t="s">
+      <c r="AC5" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="AC4" s="5" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/SampleExcelFiles/GenericTypeSampleMetadata.xlsx
+++ b/SampleExcelFiles/GenericTypeSampleMetadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/External/Projects/GitHub/UniSharper.Data.Metadata/master/SampleExcelFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70348858-380C-A845-A4EF-45BBD6065A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0F479A-0BC2-E649-9ECF-9DAF62F34A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1480" yWindow="1660" windowWidth="38400" windowHeight="19200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -902,7 +902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="20.6640625" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.6640625" style="3" customWidth="1"/>
@@ -1200,122 +1200,91 @@
       </c>
     </row>
     <row r="4" spans="1:29" ht="30" customHeight="1">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
-      <c r="Z4" s="5"/>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="5"/>
-    </row>
-    <row r="5" spans="1:29" ht="30" customHeight="1">
-      <c r="A5" s="5">
+      <c r="A4" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="5" t="b">
+      <c r="C4" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G4" s="5">
         <v>-32768</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H4" s="5">
         <v>0</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I4" s="5">
         <v>2147483647</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J4" s="5">
         <v>0</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K4" s="6">
         <v>-922337203685477</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L4" s="7">
         <v>922337203685477</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M4" s="8">
         <v>3.4548214832139799</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N4" s="5">
         <v>10.0214510024561</v>
       </c>
-      <c r="O5" s="6">
+      <c r="O4" s="6">
         <v>9.9999999999999908E+27</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="P4" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="Q5" s="5" t="s">
+      <c r="Q4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="R5" s="5" t="s">
+      <c r="R4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="S5" s="5" t="s">
+      <c r="S4" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="T5" s="5" t="s">
+      <c r="T4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="U5" s="5" t="s">
+      <c r="U4" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="V5" s="9" t="s">
+      <c r="V4" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="W5" s="5" t="s">
+      <c r="W4" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="X5" s="5" t="s">
+      <c r="X4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="Y5" s="5" t="s">
+      <c r="Y4" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="Z5" s="5" t="s">
+      <c r="Z4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AA5" s="5" t="s">
+      <c r="AA4" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="AB5" s="5" t="s">
+      <c r="AB4" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="AC5" s="5" t="s">
+      <c r="AC4" s="5" t="s">
         <v>70</v>
       </c>
     </row>
